--- a/09_teslim/sonuc-tablolari.xlsx
+++ b/09_teslim/sonuc-tablolari.xlsx
@@ -9206,13 +9206,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0207</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
+        <v>-0.0005</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5258</v>
+      </c>
       <c r="C2" t="n">
-        <v>-0.1085</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>-0.1867</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1889</v>
+      </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>

--- a/09_teslim/sonuc-tablolari.xlsx
+++ b/09_teslim/sonuc-tablolari.xlsx
@@ -1343,83 +1343,83 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A010</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4527</v>
+        <v>0.233</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4634</v>
+        <v>0.4431</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4618</v>
+        <v>0.5727</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4487</v>
+        <v>0.6861</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>B005</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.233</v>
+        <v>0.4492</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1433,11 +1433,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B006</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4431</v>
+        <v>0.4459</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1451,47 +1451,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>B007</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5727</v>
+        <v>0.426</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>B008</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6861</v>
+        <v>0.4692</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B005</t>
+          <t>B009</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4492</v>
+        <v>0.4244</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1505,50 +1505,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B006</t>
+          <t>B010</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4459</v>
+        <v>0.5595</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B007</t>
+          <t>B011</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.426</v>
+        <v>0.5238</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B008</t>
+          <t>B012</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4692</v>
+        <v>0.4691</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1559,68 +1559,68 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B009</t>
+          <t>B013</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4244</v>
+        <v>0.5712</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B010</t>
+          <t>B014</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5595</v>
+        <v>0.4387</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B011</t>
+          <t>B015</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5238</v>
+        <v>0.4857</v>
       </c>
       <c r="C64" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B012</t>
+          <t>B016</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4691</v>
+        <v>0.4819</v>
       </c>
       <c r="C65" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1631,83 +1631,83 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B013</t>
+          <t>B017</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5712</v>
+        <v>0.4856</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B014</t>
+          <t>B018</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4387</v>
+        <v>0.58</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B015</t>
+          <t>B019</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4857</v>
+        <v>0.5606</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B016</t>
+          <t>B020</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4819</v>
+        <v>0.4516</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B017</t>
+          <t>B021</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4856</v>
+        <v>0.5067</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1721,47 +1721,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B018</t>
+          <t>B022</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.58</v>
+        <v>0.4172</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B019</t>
+          <t>B023</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5606</v>
+        <v>0.3933</v>
       </c>
       <c r="C72" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B020</t>
+          <t>B024</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4516</v>
+        <v>0.433</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1775,32 +1775,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B021</t>
+          <t>B025</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5067</v>
+        <v>0.4218</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B022</t>
+          <t>B026</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4172</v>
+        <v>0.3702</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1811,11 +1811,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B023</t>
+          <t>B027</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.3933</v>
+        <v>0.2817</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1829,50 +1829,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B024</t>
+          <t>B028</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.433</v>
+        <v>0.4611</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B025</t>
+          <t>B029</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4218</v>
+        <v>0.5077</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B026</t>
+          <t>B030</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.3702</v>
+        <v>0.3916</v>
       </c>
       <c r="C79" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1883,50 +1883,50 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B027</t>
+          <t>B031</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2817</v>
+        <v>0.5727</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B028</t>
+          <t>B032</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4611</v>
+        <v>0.3639</v>
       </c>
       <c r="C81" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B029</t>
+          <t>B033</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5077</v>
+        <v>0.5053</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -1937,86 +1937,86 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B030</t>
+          <t>B034</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3916</v>
+        <v>0.4691</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B031</t>
+          <t>B035</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5727</v>
+        <v>0.2871</v>
       </c>
       <c r="C84" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B032</t>
+          <t>B036</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.3639</v>
+        <v>0.4978</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B033</t>
+          <t>B037</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5053</v>
+        <v>0.4265</v>
       </c>
       <c r="C86" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B034</t>
+          <t>B038</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4691</v>
+        <v>0.4887</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2027,11 +2027,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B035</t>
+          <t>B039</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2871</v>
+        <v>0.4493</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2045,29 +2045,29 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B036</t>
+          <t>B040</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4978</v>
+        <v>0.3086</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B037</t>
+          <t>B041</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4265</v>
+        <v>0.4284</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -2081,47 +2081,47 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B038</t>
+          <t>B042</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4887</v>
+        <v>0.2103</v>
       </c>
       <c r="C91" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B039</t>
+          <t>B043</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4493</v>
+        <v>0.4934</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B040</t>
+          <t>B044</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.3086</v>
+        <v>0.4354</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -2135,65 +2135,65 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B041</t>
+          <t>B045</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4284</v>
+        <v>0.5323</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B042</t>
+          <t>B046</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2103</v>
+        <v>0.6337</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/kararli</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B043</t>
+          <t>B047</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.4934</v>
+        <v>0.4142</v>
       </c>
       <c r="C96" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>yuksek/degisken</t>
+          <t>dusuk/degisken</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B044</t>
+          <t>B048</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4354</v>
+        <v>0.3901</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -2207,65 +2207,65 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B045</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5323</v>
+        <v>0.4527</v>
       </c>
       <c r="C98" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B046</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6337</v>
+        <v>0.4634</v>
       </c>
       <c r="C99" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>yuksek/kararli</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B047</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4142</v>
+        <v>0.4618</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>dusuk/degisken</t>
+          <t>yuksek/degisken</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B048</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3901</v>
+        <v>0.4487</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -5552,17 +5552,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A010</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>-2.48</v>
+        <v>-55.32</v>
       </c>
       <c r="D50" t="n">
-        <v>3.74</v>
+        <v>12.53</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5570,47 +5570,47 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.3537</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0.6988</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4527</v>
+        <v>0.233</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3083</v>
+        <v>0.1398</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4078</v>
+        <v>0.2096</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4527</v>
+        <v>0.233</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0.7843</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5074</v>
+        <v>0.2966</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.33</v>
+        <v>-4.14</v>
       </c>
       <c r="D51" t="n">
-        <v>0.77</v>
+        <v>1.75</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -5618,47 +5618,47 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.3857</v>
+        <v>0.329</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4634</v>
+        <v>0.4431</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3179</v>
+        <v>0.2987</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4174</v>
+        <v>0.3987</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4634</v>
+        <v>0.4431</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0.9901</v>
       </c>
       <c r="N51" t="n">
-        <v>0.517</v>
+        <v>0.4967</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0043</v>
+        <v>0.1469</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.66</v>
+        <v>12.13</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5666,47 +5666,47 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.3808</v>
+        <v>0.5712</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4618</v>
+        <v>0.5727</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3164</v>
+        <v>0.4448</v>
       </c>
       <c r="J52" t="n">
-        <v>0.416</v>
+        <v>0.5301</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0043</v>
+        <v>0.1469</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4618</v>
+        <v>0.5727</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0.9866</v>
       </c>
       <c r="N52" t="n">
-        <v>0.5155</v>
+        <v>0.6128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0043</v>
+        <v>0.3338</v>
       </c>
       <c r="C53" t="n">
-        <v>11.73</v>
+        <v>22.43</v>
       </c>
       <c r="D53" t="n">
-        <v>10.59</v>
+        <v>1.17</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5714,47 +5714,47 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.5652</v>
+        <v>0.7245</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7764</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4487</v>
+        <v>0.6861</v>
       </c>
       <c r="I53" t="n">
-        <v>0.327</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4042</v>
+        <v>0.6509</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0043</v>
+        <v>0.3338</v>
       </c>
       <c r="L53" t="n">
-        <v>0.4487</v>
+        <v>0.6861</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5261</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>B005</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>-55.32</v>
+        <v>-2.9</v>
       </c>
       <c r="D54" t="n">
-        <v>12.53</v>
+        <v>0.73</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5762,47 +5762,47 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.3474</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6988</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.233</v>
+        <v>0.4492</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1398</v>
+        <v>0.3042</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2096</v>
+        <v>0.4042</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.233</v>
+        <v>0.4492</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7843</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2966</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B006</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
       <c r="C55" t="n">
-        <v>-4.14</v>
+        <v>-6.23</v>
       </c>
       <c r="D55" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -5810,47 +5810,47 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.329</v>
+        <v>0.2979</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4431</v>
+        <v>0.4459</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2987</v>
+        <v>0.3092</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3987</v>
+        <v>0.4052</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4431</v>
+        <v>0.4459</v>
       </c>
       <c r="M55" t="n">
-        <v>0.9901</v>
+        <v>0.9698</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4967</v>
+        <v>0.4952</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>B007</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1469</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>12.13</v>
+        <v>-5.78</v>
       </c>
       <c r="D56" t="n">
-        <v>1.39</v>
+        <v>5.67</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -5858,47 +5858,47 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.5712</v>
+        <v>0.3046</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0.9732</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5727</v>
+        <v>0.426</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4448</v>
+        <v>0.286</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5301</v>
+        <v>0.3833</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1469</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5727</v>
+        <v>0.426</v>
       </c>
       <c r="M56" t="n">
-        <v>0.9866</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>0.6128</v>
+        <v>0.4847</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>B008</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3338</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>22.43</v>
+        <v>1.13</v>
       </c>
       <c r="D57" t="n">
-        <v>1.17</v>
+        <v>4.46</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -5906,47 +5906,47 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.7245</v>
+        <v>0.4074</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6861</v>
+        <v>0.4692</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.3222</v>
       </c>
       <c r="J57" t="n">
-        <v>0.6509</v>
+        <v>0.4222</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3338</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.6861</v>
+        <v>0.4692</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0.9708</v>
       </c>
       <c r="N57" t="n">
-        <v>0.7175</v>
+        <v>0.5164</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B005</t>
+          <t>B009</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>-2.9</v>
+        <v>57.02</v>
       </c>
       <c r="D58" t="n">
-        <v>0.73</v>
+        <v>23.17</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -5954,47 +5954,47 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.3474</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0.2732</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4492</v>
+        <v>0.4244</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3042</v>
+        <v>0.3546</v>
       </c>
       <c r="J58" t="n">
-        <v>0.4042</v>
+        <v>0.382</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4492</v>
+        <v>0.4244</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.9136</v>
       </c>
       <c r="N58" t="n">
-        <v>0.484</v>
+        <v>0.5374</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B006</t>
+          <t>B010</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0396</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>-6.23</v>
+        <v>13.85</v>
       </c>
       <c r="D59" t="n">
-        <v>1.19</v>
+        <v>3.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -6002,47 +6002,47 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.2979</v>
+        <v>0.5968</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4459</v>
+        <v>0.5595</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3092</v>
+        <v>0.4199</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4052</v>
+        <v>0.5117</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0396</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>0.4459</v>
+        <v>0.5595</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9698</v>
+        <v>0.9851</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4952</v>
+        <v>0.6006</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B007</t>
+          <t>B011</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
       <c r="C60" t="n">
-        <v>-5.78</v>
+        <v>7.08</v>
       </c>
       <c r="D60" t="n">
-        <v>5.67</v>
+        <v>3.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -6050,47 +6050,47 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.3046</v>
+        <v>0.496</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9732</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.426</v>
+        <v>0.5238</v>
       </c>
       <c r="I60" t="n">
-        <v>0.286</v>
+        <v>0.3864</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3833</v>
+        <v>0.4789</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
       <c r="L60" t="n">
-        <v>0.426</v>
+        <v>0.5238</v>
       </c>
       <c r="M60" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9865</v>
       </c>
       <c r="N60" t="n">
-        <v>0.4847</v>
+        <v>0.5687</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B008</t>
+          <t>B012</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="C61" t="n">
-        <v>1.13</v>
+        <v>-3.47</v>
       </c>
       <c r="D61" t="n">
-        <v>4.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -6098,47 +6098,47 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.4074</v>
+        <v>0.339</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4692</v>
+        <v>0.4691</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3222</v>
+        <v>0.3358</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4222</v>
+        <v>0.4289</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>0.4692</v>
+        <v>0.4691</v>
       </c>
       <c r="M61" t="n">
-        <v>0.9708</v>
+        <v>0.98</v>
       </c>
       <c r="N61" t="n">
-        <v>0.5164</v>
+        <v>0.5181</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B009</t>
+          <t>B013</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>0.2084</v>
       </c>
       <c r="C62" t="n">
-        <v>57.02</v>
+        <v>7.69</v>
       </c>
       <c r="D62" t="n">
-        <v>23.17</v>
+        <v>4.02</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -6146,47 +6146,47 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0.5051</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2732</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4244</v>
+        <v>0.5712</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3546</v>
+        <v>0.4557</v>
       </c>
       <c r="J62" t="n">
-        <v>0.382</v>
+        <v>0.5349</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>0.2084</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4244</v>
+        <v>0.5712</v>
       </c>
       <c r="M62" t="n">
-        <v>0.9136</v>
+        <v>0.968</v>
       </c>
       <c r="N62" t="n">
-        <v>0.5374</v>
+        <v>0.6076</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B010</t>
+          <t>B014</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.08169999999999999</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>13.85</v>
+        <v>-5.01</v>
       </c>
       <c r="D63" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -6194,47 +6194,47 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.5968</v>
+        <v>0.316</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5595</v>
+        <v>0.4387</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4199</v>
+        <v>0.2948</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5117</v>
+        <v>0.3948</v>
       </c>
       <c r="K63" t="n">
-        <v>0.08169999999999999</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5595</v>
+        <v>0.4387</v>
       </c>
       <c r="M63" t="n">
-        <v>0.9851</v>
+        <v>0.9671</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6006</v>
+        <v>0.4882</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B011</t>
+          <t>B015</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0752</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>7.08</v>
+        <v>21.03</v>
       </c>
       <c r="D64" t="n">
-        <v>3.6</v>
+        <v>11.17</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -6242,47 +6242,47 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.496</v>
+        <v>0.7037</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0.7532</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5238</v>
+        <v>0.4857</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3864</v>
+        <v>0.3618</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4789</v>
+        <v>0.4371</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0752</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5238</v>
+        <v>0.4857</v>
       </c>
       <c r="M64" t="n">
-        <v>0.9865</v>
+        <v>0.9243</v>
       </c>
       <c r="N64" t="n">
-        <v>0.5687</v>
+        <v>0.5466</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B012</t>
+          <t>B016</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0298</v>
       </c>
       <c r="C65" t="n">
-        <v>-3.47</v>
+        <v>1.68</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.45</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6290,47 +6290,47 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.339</v>
+        <v>0.4156</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4691</v>
+        <v>0.4819</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3358</v>
+        <v>0.3396</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4289</v>
+        <v>0.4366</v>
       </c>
       <c r="K65" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0298</v>
       </c>
       <c r="L65" t="n">
-        <v>0.4691</v>
+        <v>0.4819</v>
       </c>
       <c r="M65" t="n">
-        <v>0.98</v>
+        <v>0.739</v>
       </c>
       <c r="N65" t="n">
-        <v>0.5181</v>
+        <v>0.4814</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B013</t>
+          <t>B017</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.2084</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>7.69</v>
+        <v>4.44</v>
       </c>
       <c r="D66" t="n">
-        <v>4.02</v>
+        <v>4.09</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6338,47 +6338,47 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.5051</v>
+        <v>0.4567</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5712</v>
+        <v>0.4856</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4557</v>
+        <v>0.337</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5349</v>
+        <v>0.437</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2084</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5712</v>
+        <v>0.4856</v>
       </c>
       <c r="M66" t="n">
-        <v>0.968</v>
+        <v>0.9683</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6076</v>
+        <v>0.5306999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B014</t>
+          <t>B018</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>0.2171</v>
       </c>
       <c r="C67" t="n">
-        <v>-5.01</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -6386,47 +6386,47 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.316</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4387</v>
+        <v>0.58</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2948</v>
+        <v>0.4654</v>
       </c>
       <c r="J67" t="n">
-        <v>0.3948</v>
+        <v>0.5436</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>0.2171</v>
       </c>
       <c r="L67" t="n">
-        <v>0.4387</v>
+        <v>0.58</v>
       </c>
       <c r="M67" t="n">
-        <v>0.9671</v>
+        <v>0.9807</v>
       </c>
       <c r="N67" t="n">
-        <v>0.4882</v>
+        <v>0.6181</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B015</t>
+          <t>B019</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>0.0354</v>
       </c>
       <c r="C68" t="n">
-        <v>21.03</v>
+        <v>26.48</v>
       </c>
       <c r="D68" t="n">
-        <v>11.17</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -6434,47 +6434,47 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.7037</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7532</v>
+        <v>0.8616</v>
       </c>
       <c r="H68" t="n">
-        <v>0.4857</v>
+        <v>0.5606</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3618</v>
+        <v>0.4255</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4371</v>
+        <v>0.5081</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>0.0354</v>
       </c>
       <c r="L68" t="n">
-        <v>0.4857</v>
+        <v>0.5606</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9243</v>
+        <v>0.9879</v>
       </c>
       <c r="N68" t="n">
-        <v>0.5466</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B016</t>
+          <t>B020</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0298</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>1.68</v>
+        <v>-2.42</v>
       </c>
       <c r="D69" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -6482,47 +6482,47 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.4156</v>
+        <v>0.3546</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.4819</v>
+        <v>0.4516</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3396</v>
+        <v>0.3064</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4366</v>
+        <v>0.4064</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0298</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.4819</v>
+        <v>0.4516</v>
       </c>
       <c r="M69" t="n">
-        <v>0.739</v>
+        <v>0.9877</v>
       </c>
       <c r="N69" t="n">
-        <v>0.4814</v>
+        <v>0.5039</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B017</t>
+          <t>B021</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>0.0102</v>
       </c>
       <c r="C70" t="n">
-        <v>4.44</v>
+        <v>8.01</v>
       </c>
       <c r="D70" t="n">
-        <v>4.09</v>
+        <v>2.98</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6530,47 +6530,47 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.4567</v>
+        <v>0.5099</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4856</v>
+        <v>0.5067</v>
       </c>
       <c r="I70" t="n">
-        <v>0.337</v>
+        <v>0.3581</v>
       </c>
       <c r="J70" t="n">
-        <v>0.437</v>
+        <v>0.457</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>0.0102</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4856</v>
+        <v>0.5067</v>
       </c>
       <c r="M70" t="n">
-        <v>0.9683</v>
+        <v>0.989</v>
       </c>
       <c r="N70" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5538</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B018</t>
+          <t>B022</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.2171</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>8.869999999999999</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>4.33</v>
+        <v>4.81</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6578,47 +6578,47 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.2513</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0.58</v>
+        <v>0.4172</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4654</v>
+        <v>0.2754</v>
       </c>
       <c r="J71" t="n">
-        <v>0.5436</v>
+        <v>0.3754</v>
       </c>
       <c r="K71" t="n">
-        <v>0.2171</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.58</v>
+        <v>0.4172</v>
       </c>
       <c r="M71" t="n">
-        <v>0.9807</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>0.6181</v>
+        <v>0.4662</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B019</t>
+          <t>B023</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0354</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>26.48</v>
+        <v>-7.38</v>
       </c>
       <c r="D72" t="n">
-        <v>8.460000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6626,47 +6626,47 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.2808</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8616</v>
+        <v>0.8988</v>
       </c>
       <c r="H72" t="n">
-        <v>0.5606</v>
+        <v>0.3933</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4255</v>
+        <v>0.264</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5081</v>
+        <v>0.3539</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0354</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5606</v>
+        <v>0.3933</v>
       </c>
       <c r="M72" t="n">
-        <v>0.9879</v>
+        <v>0.9659</v>
       </c>
       <c r="N72" t="n">
-        <v>0.616</v>
+        <v>0.4572</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B020</t>
+          <t>B024</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="C73" t="n">
-        <v>-2.42</v>
+        <v>-6.47</v>
       </c>
       <c r="D73" t="n">
-        <v>2.78</v>
+        <v>0.19</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6674,47 +6674,47 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.3546</v>
+        <v>0.2943</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.4516</v>
+        <v>0.433</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3064</v>
+        <v>0.2905</v>
       </c>
       <c r="J73" t="n">
-        <v>0.4064</v>
+        <v>0.3901</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="L73" t="n">
-        <v>0.4516</v>
+        <v>0.433</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9877</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>0.5039</v>
+        <v>0.4896</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B021</t>
+          <t>B025</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0102</v>
+        <v>0.0073</v>
       </c>
       <c r="C74" t="n">
-        <v>8.01</v>
+        <v>-2.76</v>
       </c>
       <c r="D74" t="n">
-        <v>2.98</v>
+        <v>7.29</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -6722,47 +6722,47 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.5099</v>
+        <v>0.3495</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0.9084</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5067</v>
+        <v>0.4218</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3581</v>
+        <v>0.2902</v>
       </c>
       <c r="J74" t="n">
-        <v>0.457</v>
+        <v>0.3803</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0102</v>
+        <v>0.0073</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5067</v>
+        <v>0.4218</v>
       </c>
       <c r="M74" t="n">
-        <v>0.989</v>
+        <v>0.9816</v>
       </c>
       <c r="N74" t="n">
-        <v>0.5538</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B022</t>
+          <t>B026</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>0.2656</v>
       </c>
       <c r="C75" t="n">
-        <v>-9.359999999999999</v>
+        <v>-37.64</v>
       </c>
       <c r="D75" t="n">
-        <v>4.81</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -6770,47 +6770,47 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.2513</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0.8448</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4172</v>
+        <v>0.3702</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2754</v>
+        <v>0.3018</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3754</v>
+        <v>0.3597</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>0.2656</v>
       </c>
       <c r="L75" t="n">
-        <v>0.4172</v>
+        <v>0.3702</v>
       </c>
       <c r="M75" t="n">
-        <v>0.9540999999999999</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>0.4662</v>
+        <v>0.4486</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B023</t>
+          <t>B027</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.38</v>
+        <v>-8.59</v>
       </c>
       <c r="D76" t="n">
-        <v>7.53</v>
+        <v>15.44</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6818,47 +6818,47 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.2808</v>
+        <v>0.2627</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8988</v>
+        <v>0.5824</v>
       </c>
       <c r="H76" t="n">
-        <v>0.3933</v>
+        <v>0.2817</v>
       </c>
       <c r="I76" t="n">
-        <v>0.264</v>
+        <v>0.1953</v>
       </c>
       <c r="J76" t="n">
-        <v>0.3539</v>
+        <v>0.2535</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3933</v>
+        <v>0.2817</v>
       </c>
       <c r="M76" t="n">
-        <v>0.9659</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>0.4572</v>
+        <v>0.3953</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B024</t>
+          <t>B028</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0045</v>
+        <v>0.0725</v>
       </c>
       <c r="C77" t="n">
-        <v>-6.47</v>
+        <v>-5.38</v>
       </c>
       <c r="D77" t="n">
-        <v>0.19</v>
+        <v>4.56</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6866,47 +6866,47 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.2943</v>
+        <v>0.3105</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.433</v>
+        <v>0.4611</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2905</v>
+        <v>0.3294</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3901</v>
+        <v>0.4222</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0045</v>
+        <v>0.0725</v>
       </c>
       <c r="L77" t="n">
-        <v>0.433</v>
+        <v>0.4611</v>
       </c>
       <c r="M77" t="n">
         <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>0.4896</v>
+        <v>0.5149</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B025</t>
+          <t>B029</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0073</v>
+        <v>0.0524</v>
       </c>
       <c r="C78" t="n">
-        <v>-2.76</v>
+        <v>5.38</v>
       </c>
       <c r="D78" t="n">
-        <v>7.29</v>
+        <v>0.68</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -6914,47 +6914,47 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.3495</v>
+        <v>0.4707</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9084</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.4218</v>
+        <v>0.5077</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2902</v>
+        <v>0.3674</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3803</v>
+        <v>0.4622</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0073</v>
+        <v>0.0524</v>
       </c>
       <c r="L78" t="n">
-        <v>0.4218</v>
+        <v>0.5077</v>
       </c>
       <c r="M78" t="n">
-        <v>0.9816</v>
+        <v>0.835</v>
       </c>
       <c r="N78" t="n">
-        <v>0.485</v>
+        <v>0.5239</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B026</t>
+          <t>B030</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.2656</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>-37.64</v>
+        <v>-1.06</v>
       </c>
       <c r="D79" t="n">
-        <v>8.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6962,47 +6962,47 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>0.3748</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8448</v>
+        <v>0.8</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3702</v>
+        <v>0.3916</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3018</v>
+        <v>0.2724</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3597</v>
+        <v>0.3524</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2656</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3702</v>
+        <v>0.3916</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="N79" t="n">
-        <v>0.4486</v>
+        <v>0.4722</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B027</t>
+          <t>B031</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>0.0559</v>
       </c>
       <c r="C80" t="n">
-        <v>-8.59</v>
+        <v>18.23</v>
       </c>
       <c r="D80" t="n">
-        <v>15.44</v>
+        <v>1.24</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -7010,47 +7010,47 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.2627</v>
+        <v>0.662</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5824</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.2817</v>
+        <v>0.5727</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1953</v>
+        <v>0.4266</v>
       </c>
       <c r="J80" t="n">
-        <v>0.2535</v>
+        <v>0.521</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>0.0559</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2817</v>
+        <v>0.5727</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0.9765</v>
       </c>
       <c r="N80" t="n">
-        <v>0.3953</v>
+        <v>0.6107</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B028</t>
+          <t>B032</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0725</v>
+        <v>0.1258</v>
       </c>
       <c r="C81" t="n">
-        <v>-5.38</v>
+        <v>-7.18</v>
       </c>
       <c r="D81" t="n">
-        <v>4.56</v>
+        <v>12.95</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -7058,47 +7058,47 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.3105</v>
+        <v>0.2837</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4611</v>
+        <v>0.3639</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3294</v>
+        <v>0.2844</v>
       </c>
       <c r="J81" t="n">
-        <v>0.4222</v>
+        <v>0.34</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0725</v>
+        <v>0.1258</v>
       </c>
       <c r="L81" t="n">
-        <v>0.4611</v>
+        <v>0.3639</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0.9808</v>
       </c>
       <c r="N81" t="n">
-        <v>0.5149</v>
+        <v>0.4554</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B029</t>
+          <t>B033</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0524</v>
+        <v>0.1085</v>
       </c>
       <c r="C82" t="n">
-        <v>5.38</v>
+        <v>1.12</v>
       </c>
       <c r="D82" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -7106,47 +7106,47 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.4707</v>
+        <v>0.4073</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.5077</v>
+        <v>0.5053</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3674</v>
+        <v>0.3764</v>
       </c>
       <c r="J82" t="n">
-        <v>0.4622</v>
+        <v>0.4656</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0524</v>
+        <v>0.1085</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5077</v>
+        <v>0.5053</v>
       </c>
       <c r="M82" t="n">
-        <v>0.835</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5239</v>
+        <v>0.5547</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B030</t>
+          <t>B034</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.06</v>
+        <v>10.55</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>9.66</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -7154,47 +7154,47 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.3748</v>
+        <v>0.5477</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8</v>
+        <v>0.8136</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3916</v>
+        <v>0.4691</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2724</v>
+        <v>0.3499</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3524</v>
+        <v>0.4267</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="L83" t="n">
-        <v>0.3916</v>
+        <v>0.4691</v>
       </c>
       <c r="M83" t="n">
-        <v>0.9986</v>
+        <v>0.9839</v>
       </c>
       <c r="N83" t="n">
-        <v>0.4722</v>
+        <v>0.5376</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B031</t>
+          <t>B035</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0559</v>
+        <v>0.2852</v>
       </c>
       <c r="C84" t="n">
-        <v>18.23</v>
+        <v>-2.31</v>
       </c>
       <c r="D84" t="n">
-        <v>1.24</v>
+        <v>24.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -7202,47 +7202,47 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.662</v>
+        <v>0.3562</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5727</v>
+        <v>0.2871</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4266</v>
+        <v>0.2935</v>
       </c>
       <c r="J84" t="n">
-        <v>0.521</v>
+        <v>0.2869</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0559</v>
+        <v>0.2852</v>
       </c>
       <c r="L84" t="n">
-        <v>0.5727</v>
+        <v>0.2871</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9765</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>0.6107</v>
+        <v>0.4364</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B032</t>
+          <t>B036</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.1258</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.18</v>
+        <v>8.51</v>
       </c>
       <c r="D85" t="n">
-        <v>12.95</v>
+        <v>5.6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -7250,47 +7250,47 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.2837</v>
+        <v>0.5173</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.976</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3639</v>
+        <v>0.4978</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2844</v>
+        <v>0.3504</v>
       </c>
       <c r="J85" t="n">
-        <v>0.34</v>
+        <v>0.448</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1258</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.3639</v>
+        <v>0.4978</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9808</v>
+        <v>0.8544</v>
       </c>
       <c r="N85" t="n">
-        <v>0.4554</v>
+        <v>0.5213</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B033</t>
+          <t>B037</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.1085</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>1.12</v>
+        <v>-7.47</v>
       </c>
       <c r="D86" t="n">
-        <v>0.45</v>
+        <v>4.24</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -7298,47 +7298,47 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.4073</v>
+        <v>0.2794</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5053</v>
+        <v>0.4265</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3764</v>
+        <v>0.2838</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4656</v>
+        <v>0.3838</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1085</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5053</v>
+        <v>0.4265</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0.9876</v>
       </c>
       <c r="N86" t="n">
-        <v>0.5547</v>
+        <v>0.4813</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B034</t>
+          <t>B038</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0458</v>
+        <v>0.0706</v>
       </c>
       <c r="C87" t="n">
-        <v>10.55</v>
+        <v>0.32</v>
       </c>
       <c r="D87" t="n">
-        <v>9.66</v>
+        <v>1.09</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -7346,47 +7346,47 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.5477</v>
+        <v>0.3954</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8136</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.4691</v>
+        <v>0.4887</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3499</v>
+        <v>0.3539</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4267</v>
+        <v>0.4469</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0458</v>
+        <v>0.0706</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4691</v>
+        <v>0.4887</v>
       </c>
       <c r="M87" t="n">
-        <v>0.9839</v>
+        <v>0.9217</v>
       </c>
       <c r="N87" t="n">
-        <v>0.5376</v>
+        <v>0.5241</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B035</t>
+          <t>B039</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2852</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>-2.31</v>
+        <v>-2.89</v>
       </c>
       <c r="D88" t="n">
-        <v>24.5</v>
+        <v>0.89</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -7394,47 +7394,47 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.3562</v>
+        <v>0.3476</v>
       </c>
       <c r="G88" t="n">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2871</v>
+        <v>0.4493</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2935</v>
+        <v>0.3043</v>
       </c>
       <c r="J88" t="n">
-        <v>0.2869</v>
+        <v>0.4043</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2852</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0.2871</v>
+        <v>0.4493</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0.9778</v>
       </c>
       <c r="N88" t="n">
-        <v>0.4364</v>
+        <v>0.4998</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B036</t>
+          <t>B040</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>8.51</v>
+        <v>-19.98</v>
       </c>
       <c r="D89" t="n">
-        <v>5.6</v>
+        <v>9.19</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -7442,47 +7442,47 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.5173</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>0.976</v>
+        <v>0.8324</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4978</v>
+        <v>0.3086</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3504</v>
+        <v>0.1944</v>
       </c>
       <c r="J89" t="n">
-        <v>0.448</v>
+        <v>0.2777</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0.4978</v>
+        <v>0.3086</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8544</v>
+        <v>0.9621</v>
       </c>
       <c r="N89" t="n">
-        <v>0.5213</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B037</t>
+          <t>B041</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.47</v>
+        <v>-7.09</v>
       </c>
       <c r="D90" t="n">
-        <v>4.24</v>
+        <v>0.45</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -7490,47 +7490,47 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.2794</v>
+        <v>0.2851</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4265</v>
+        <v>0.4284</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2838</v>
+        <v>0.2855</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3838</v>
+        <v>0.3855</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4265</v>
+        <v>0.4284</v>
       </c>
       <c r="M90" t="n">
-        <v>0.9876</v>
+        <v>0.9937</v>
       </c>
       <c r="N90" t="n">
-        <v>0.4813</v>
+        <v>0.4843</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B038</t>
+          <t>B042</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0706</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.32</v>
+        <v>-9.6</v>
       </c>
       <c r="D91" t="n">
-        <v>1.09</v>
+        <v>20.42</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -7538,47 +7538,47 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.3954</v>
+        <v>0.2477</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0.3832</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4887</v>
+        <v>0.2103</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3539</v>
+        <v>0.151</v>
       </c>
       <c r="J91" t="n">
-        <v>0.4469</v>
+        <v>0.1893</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0706</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0.4887</v>
+        <v>0.2103</v>
       </c>
       <c r="M91" t="n">
-        <v>0.9217</v>
+        <v>0.967</v>
       </c>
       <c r="N91" t="n">
-        <v>0.5241</v>
+        <v>0.3444</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B039</t>
+          <t>B043</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>0.1055</v>
       </c>
       <c r="C92" t="n">
-        <v>-2.89</v>
+        <v>-1.09</v>
       </c>
       <c r="D92" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -7586,47 +7586,47 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.3476</v>
+        <v>0.3744</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>0.4493</v>
+        <v>0.4934</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3043</v>
+        <v>0.3651</v>
       </c>
       <c r="J92" t="n">
-        <v>0.4043</v>
+        <v>0.4545</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>0.1055</v>
       </c>
       <c r="L92" t="n">
-        <v>0.4493</v>
+        <v>0.4934</v>
       </c>
       <c r="M92" t="n">
-        <v>0.9778</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>0.4998</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B040</t>
+          <t>B044</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.0649</v>
       </c>
       <c r="C93" t="n">
-        <v>-19.98</v>
+        <v>0.01</v>
       </c>
       <c r="D93" t="n">
-        <v>9.19</v>
+        <v>8.74</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -7634,47 +7634,47 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.3908</v>
       </c>
       <c r="G93" t="n">
-        <v>0.8324</v>
+        <v>0.8504</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3086</v>
+        <v>0.4354</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1944</v>
+        <v>0.3198</v>
       </c>
       <c r="J93" t="n">
-        <v>0.2777</v>
+        <v>0.3983</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>0.0649</v>
       </c>
       <c r="L93" t="n">
-        <v>0.3086</v>
+        <v>0.4354</v>
       </c>
       <c r="M93" t="n">
-        <v>0.9621</v>
+        <v>0.97</v>
       </c>
       <c r="N93" t="n">
-        <v>0.3869</v>
+        <v>0.5008</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B041</t>
+          <t>B045</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.09</v>
+        <v>45.38</v>
       </c>
       <c r="D94" t="n">
-        <v>0.45</v>
+        <v>15.08</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -7682,47 +7682,47 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.2851</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.5968</v>
       </c>
       <c r="H94" t="n">
-        <v>0.4284</v>
+        <v>0.5323</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2855</v>
+        <v>0.4194</v>
       </c>
       <c r="J94" t="n">
-        <v>0.3855</v>
+        <v>0.479</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0.4284</v>
+        <v>0.5323</v>
       </c>
       <c r="M94" t="n">
-        <v>0.9937</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="N94" t="n">
-        <v>0.4843</v>
+        <v>0.5995</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B042</t>
+          <t>B046</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>-9.6</v>
+        <v>36.46</v>
       </c>
       <c r="D95" t="n">
-        <v>20.42</v>
+        <v>5.81</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -7730,47 +7730,47 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.2477</v>
+        <v>0.9334</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3832</v>
+        <v>0.9676</v>
       </c>
       <c r="H95" t="n">
-        <v>0.2103</v>
+        <v>0.6337</v>
       </c>
       <c r="I95" t="n">
-        <v>0.151</v>
+        <v>0.4735</v>
       </c>
       <c r="J95" t="n">
-        <v>0.1893</v>
+        <v>0.5703</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0.2103</v>
+        <v>0.6337</v>
       </c>
       <c r="M95" t="n">
-        <v>0.967</v>
+        <v>0.9823</v>
       </c>
       <c r="N95" t="n">
-        <v>0.3444</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B043</t>
+          <t>B047</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.1055</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.09</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="D96" t="n">
-        <v>0.48</v>
+        <v>5.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -7778,47 +7778,47 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.3744</v>
+        <v>0.2623</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4934</v>
+        <v>0.4142</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3651</v>
+        <v>0.2747</v>
       </c>
       <c r="J96" t="n">
-        <v>0.4545</v>
+        <v>0.3727</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1055</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.4934</v>
+        <v>0.4142</v>
       </c>
       <c r="M96" t="n">
         <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>0.544</v>
+        <v>0.4747</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B044</t>
+          <t>B048</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0649</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01</v>
+        <v>-4.49</v>
       </c>
       <c r="D97" t="n">
-        <v>8.74</v>
+        <v>8.84</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -7826,47 +7826,47 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.3908</v>
+        <v>0.3238</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8504</v>
+        <v>0.8464</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4354</v>
+        <v>0.3901</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3198</v>
+        <v>0.2664</v>
       </c>
       <c r="J97" t="n">
-        <v>0.3983</v>
+        <v>0.3511</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0649</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0.4354</v>
+        <v>0.3901</v>
       </c>
       <c r="M97" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N97" t="n">
-        <v>0.5008</v>
+        <v>0.4664</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B045</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="C98" t="n">
-        <v>45.38</v>
+        <v>-2.48</v>
       </c>
       <c r="D98" t="n">
-        <v>15.08</v>
+        <v>3.74</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -7874,47 +7874,47 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0.3537</v>
       </c>
       <c r="G98" t="n">
-        <v>0.5968</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.5323</v>
+        <v>0.4527</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4194</v>
+        <v>0.3083</v>
       </c>
       <c r="J98" t="n">
-        <v>0.479</v>
+        <v>0.4078</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="L98" t="n">
-        <v>0.5323</v>
+        <v>0.4527</v>
       </c>
       <c r="M98" t="n">
-        <v>0.9006999999999999</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>0.5995</v>
+        <v>0.5074</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B046</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="C99" t="n">
-        <v>36.46</v>
+        <v>-0.33</v>
       </c>
       <c r="D99" t="n">
-        <v>5.81</v>
+        <v>0.77</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -7922,47 +7922,47 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.9334</v>
+        <v>0.3857</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9676</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0.6337</v>
+        <v>0.4634</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4735</v>
+        <v>0.3179</v>
       </c>
       <c r="J99" t="n">
-        <v>0.5703</v>
+        <v>0.4174</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="L99" t="n">
-        <v>0.6337</v>
+        <v>0.4634</v>
       </c>
       <c r="M99" t="n">
-        <v>0.9823</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>0.67</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B047</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="C100" t="n">
-        <v>-8.619999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="D100" t="n">
-        <v>5.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -7970,47 +7970,47 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.2623</v>
+        <v>0.3808</v>
       </c>
       <c r="G100" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4142</v>
+        <v>0.4618</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2747</v>
+        <v>0.3164</v>
       </c>
       <c r="J100" t="n">
-        <v>0.3727</v>
+        <v>0.416</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="L100" t="n">
-        <v>0.4142</v>
+        <v>0.4618</v>
       </c>
       <c r="M100" t="n">
         <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>0.4747</v>
+        <v>0.5155</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B048</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="C101" t="n">
-        <v>-4.49</v>
+        <v>11.73</v>
       </c>
       <c r="D101" t="n">
-        <v>8.84</v>
+        <v>10.59</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -8018,31 +8018,31 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.3238</v>
+        <v>0.5652</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8464</v>
+        <v>0.7764</v>
       </c>
       <c r="H101" t="n">
-        <v>0.3901</v>
+        <v>0.4487</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2664</v>
+        <v>0.327</v>
       </c>
       <c r="J101" t="n">
-        <v>0.3511</v>
+        <v>0.4042</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="L101" t="n">
-        <v>0.3901</v>
+        <v>0.4487</v>
       </c>
       <c r="M101" t="n">
         <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>0.4664</v>
+        <v>0.5261</v>
       </c>
     </row>
   </sheetData>
@@ -10471,93 +10471,93 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A010</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4527</v>
+        <v>0.233</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0.6988</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4527</v>
+        <v>0.2329</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4634</v>
+        <v>0.4431</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4633</v>
+        <v>0.443</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4618</v>
+        <v>0.5727</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4617</v>
+        <v>0.5727</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0043</v>
+        <v>0.1469</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4487</v>
+        <v>0.6861</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7764</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4486</v>
+        <v>0.6861</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0043</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>B005</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.233</v>
+        <v>0.4492</v>
       </c>
       <c r="C54" t="n">
-        <v>0.6988</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2329</v>
+        <v>0.4491</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -10566,74 +10566,74 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B006</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4431</v>
+        <v>0.4459</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0.443</v>
+        <v>0.4458</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>B007</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5727</v>
+        <v>0.426</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0.9732</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5727</v>
+        <v>0.4259</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>B008</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6861</v>
+        <v>0.4692</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6861</v>
+        <v>0.4691</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B005</t>
+          <t>B009</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4492</v>
+        <v>0.4244</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4491</v>
+        <v>0.4244</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -10642,321 +10642,321 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B006</t>
+          <t>B010</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4459</v>
+        <v>0.5595</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4458</v>
+        <v>0.5595</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0396</v>
+        <v>0.08169999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B007</t>
+          <t>B011</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.426</v>
+        <v>0.5238</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9732</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4259</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B008</t>
+          <t>B012</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4692</v>
+        <v>0.4691</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4691</v>
+        <v>0.469</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.06809999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B009</t>
+          <t>B013</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4244</v>
+        <v>0.5712</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4244</v>
+        <v>0.5712</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>0.2084</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B010</t>
+          <t>B014</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5595</v>
+        <v>0.4387</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0.5595</v>
+        <v>0.4387</v>
       </c>
       <c r="E63" t="n">
-        <v>0.08169999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B011</t>
+          <t>B015</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5238</v>
+        <v>0.4857</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.7532</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.4856</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B012</t>
+          <t>B016</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4691</v>
+        <v>0.4819</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0.469</v>
+        <v>0.4818</v>
       </c>
       <c r="E65" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B013</t>
+          <t>B017</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5712</v>
+        <v>0.4856</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5712</v>
+        <v>0.4856</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B014</t>
+          <t>B018</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4387</v>
+        <v>0.58</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0.4387</v>
+        <v>0.5799</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>0.2171</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B015</t>
+          <t>B019</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4857</v>
+        <v>0.5606</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7532</v>
+        <v>0.8616</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4856</v>
+        <v>0.5606</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>0.0354</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B016</t>
+          <t>B020</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4819</v>
+        <v>0.4516</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4818</v>
+        <v>0.4515</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B017</t>
+          <t>B021</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4856</v>
+        <v>0.5067</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4856</v>
+        <v>0.5067</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B018</t>
+          <t>B022</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.58</v>
+        <v>0.4172</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5799</v>
+        <v>0.4171</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B019</t>
+          <t>B023</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5606</v>
+        <v>0.3933</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8616</v>
+        <v>0.8988</v>
       </c>
       <c r="D72" t="n">
-        <v>0.5606</v>
+        <v>0.3932</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B020</t>
+          <t>B024</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4516</v>
+        <v>0.433</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4515</v>
+        <v>0.4329</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B021</t>
+          <t>B025</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5067</v>
+        <v>0.4218</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0.9084</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5067</v>
+        <v>0.4217</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0102</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B022</t>
+          <t>B026</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4172</v>
+        <v>0.3702</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0.8448</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4171</v>
+        <v>0.3701</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -10965,17 +10965,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B023</t>
+          <t>B027</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.3933</v>
+        <v>0.2817</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8988</v>
+        <v>0.5824</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3932</v>
+        <v>0.2817</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -10984,55 +10984,55 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B024</t>
+          <t>B028</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.433</v>
+        <v>0.4611</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4329</v>
+        <v>0.461</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0045</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B025</t>
+          <t>B029</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4218</v>
+        <v>0.5077</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9084</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4217</v>
+        <v>0.5077</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0073</v>
+        <v>0.0524</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B026</t>
+          <t>B030</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.3702</v>
+        <v>0.3916</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8448</v>
+        <v>0.8</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3701</v>
+        <v>0.3916</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -11041,188 +11041,188 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B027</t>
+          <t>B031</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2817</v>
+        <v>0.5727</v>
       </c>
       <c r="C80" t="n">
-        <v>0.5824</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2817</v>
+        <v>0.5726</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>0.0559</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B028</t>
+          <t>B032</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4611</v>
+        <v>0.3639</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>0.461</v>
+        <v>0.3638</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0725</v>
+        <v>0.1258</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B029</t>
+          <t>B033</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5077</v>
+        <v>0.5053</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0.5077</v>
+        <v>0.5053</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0524</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B030</t>
+          <t>B034</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3916</v>
+        <v>0.4691</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8</v>
+        <v>0.8136</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3916</v>
+        <v>0.469</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B031</t>
+          <t>B035</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5727</v>
+        <v>0.2871</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0.3562</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5726</v>
+        <v>0.2871</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0559</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B032</t>
+          <t>B036</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.3639</v>
+        <v>0.4978</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.976</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3638</v>
+        <v>0.4978</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B033</t>
+          <t>B037</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5053</v>
+        <v>0.4265</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5053</v>
+        <v>0.4265</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B034</t>
+          <t>B038</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4691</v>
+        <v>0.4887</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8136</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0.469</v>
+        <v>0.4887</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0458</v>
+        <v>0.0706</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B035</t>
+          <t>B039</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2871</v>
+        <v>0.4493</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3562</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2871</v>
+        <v>0.4492</v>
       </c>
       <c r="E88" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B036</t>
+          <t>B040</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4978</v>
+        <v>0.3086</v>
       </c>
       <c r="C89" t="n">
-        <v>0.976</v>
+        <v>0.8324</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4978</v>
+        <v>0.3085</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -11231,17 +11231,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B037</t>
+          <t>B041</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4265</v>
+        <v>0.4284</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4265</v>
+        <v>0.4284</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11250,74 +11250,74 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B038</t>
+          <t>B042</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4887</v>
+        <v>0.2103</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0.3832</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4887</v>
+        <v>0.2103</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B039</t>
+          <t>B043</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4493</v>
+        <v>0.4934</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4492</v>
+        <v>0.4933</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.1055</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B040</t>
+          <t>B044</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.3086</v>
+        <v>0.4354</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8324</v>
+        <v>0.8504</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3085</v>
+        <v>0.4354</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B041</t>
+          <t>B045</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4284</v>
+        <v>0.5323</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4284</v>
+        <v>0.5323</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -11326,17 +11326,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B042</t>
+          <t>B046</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2103</v>
+        <v>0.6337</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3832</v>
+        <v>0.9676</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2103</v>
+        <v>0.6337</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -11345,115 +11345,115 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B043</t>
+          <t>B047</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.4934</v>
+        <v>0.4142</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4933</v>
+        <v>0.4141</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B044</t>
+          <t>B048</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4354</v>
+        <v>0.3901</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8504</v>
+        <v>0.8464</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4354</v>
+        <v>0.3901</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B045</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5323</v>
+        <v>0.4527</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5323</v>
+        <v>0.4527</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B046</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6337</v>
+        <v>0.4634</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9676</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0.6337</v>
+        <v>0.4633</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B047</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4142</v>
+        <v>0.4618</v>
       </c>
       <c r="C100" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4141</v>
+        <v>0.4617</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B048</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3901</v>
+        <v>0.4487</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8464</v>
+        <v>0.7764</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3901</v>
+        <v>0.4486</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="102">
